--- a/src/test/resources/testdata/Modules/11_KYCSubmission/KYCSubmission/01_KYCTest.xlsx
+++ b/src/test/resources/testdata/Modules/11_KYCSubmission/KYCSubmission/01_KYCTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\11_KYCSubmission\KYCSubmission\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80050E08-101F-462A-A781-D6E9F49595B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7ED0D2D-9E60-4A77-A672-6271DDCCD451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -65,9 +65,6 @@
     <t>EXPECTED_KEY</t>
   </si>
   <si>
-    <t>2602000013</t>
-  </si>
-  <si>
     <t>KycSubmissionTest_01</t>
   </si>
   <si>
@@ -2611,6 +2608,9 @@
 select_spousegenerdropvalue
 clickon_submitbtn
 verify_snackbartext</t>
+  </si>
+  <si>
+    <t>2603000013</t>
   </si>
 </sst>
 </file>
@@ -3563,25 +3563,25 @@
         <v>3</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H1" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>100</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>101</v>
       </c>
       <c r="M1" s="7" t="s">
         <v>8</v>
@@ -3595,25 +3595,25 @@
     </row>
     <row r="2" spans="1:15" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
@@ -3622,7 +3622,7 @@
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
       <c r="N2" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>5</v>
@@ -3630,19 +3630,19 @@
     </row>
     <row r="3" spans="1:15" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
@@ -3652,7 +3652,7 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="N3" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>5</v>
@@ -3660,19 +3660,19 @@
     </row>
     <row r="4" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -3683,7 +3683,7 @@
       <c r="L4" s="1"/>
       <c r="M4" s="5"/>
       <c r="N4" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>5</v>
@@ -3691,24 +3691,24 @@
     </row>
     <row r="5" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -3716,7 +3716,7 @@
       <c r="L5" s="1"/>
       <c r="M5" s="5"/>
       <c r="N5" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>5</v>
@@ -3724,19 +3724,19 @@
     </row>
     <row r="6" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
@@ -3747,7 +3747,7 @@
       <c r="L6" s="1"/>
       <c r="M6" s="5"/>
       <c r="N6" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>5</v>
@@ -3755,19 +3755,19 @@
     </row>
     <row r="7" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -3778,7 +3778,7 @@
       <c r="L7" s="1"/>
       <c r="M7" s="5"/>
       <c r="N7" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>5</v>
@@ -3786,19 +3786,19 @@
     </row>
     <row r="8" spans="1:15" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -3809,7 +3809,7 @@
       <c r="L8" s="1"/>
       <c r="M8" s="5"/>
       <c r="N8" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>5</v>
@@ -3817,19 +3817,19 @@
     </row>
     <row r="9" spans="1:15" ht="174" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -3840,7 +3840,7 @@
       <c r="L9" s="1"/>
       <c r="M9" s="5"/>
       <c r="N9" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>5</v>
@@ -3848,19 +3848,19 @@
     </row>
     <row r="10" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -3871,7 +3871,7 @@
       <c r="L10" s="1"/>
       <c r="M10" s="5"/>
       <c r="N10" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>5</v>
@@ -3879,19 +3879,19 @@
     </row>
     <row r="11" spans="1:15" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -3902,7 +3902,7 @@
       <c r="L11" s="1"/>
       <c r="M11" s="5"/>
       <c r="N11" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>5</v>
@@ -3910,19 +3910,19 @@
     </row>
     <row r="12" spans="1:15" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -3933,7 +3933,7 @@
       <c r="L12" s="1"/>
       <c r="M12" s="5"/>
       <c r="N12" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>5</v>
@@ -3941,19 +3941,19 @@
     </row>
     <row r="13" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -3964,7 +3964,7 @@
       <c r="L13" s="1"/>
       <c r="M13" s="5"/>
       <c r="N13" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O13" s="1" t="s">
         <v>5</v>
@@ -3972,19 +3972,19 @@
     </row>
     <row r="14" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -3995,7 +3995,7 @@
       <c r="L14" s="1"/>
       <c r="M14" s="5"/>
       <c r="N14" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O14" s="1" t="s">
         <v>5</v>
@@ -4003,19 +4003,19 @@
     </row>
     <row r="15" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -4026,7 +4026,7 @@
       <c r="L15" s="1"/>
       <c r="M15" s="5"/>
       <c r="N15" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>5</v>
@@ -4034,19 +4034,19 @@
     </row>
     <row r="16" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>37</v>
-      </c>
       <c r="D16" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -4057,7 +4057,7 @@
       <c r="L16" s="1"/>
       <c r="M16" s="5"/>
       <c r="N16" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O16" s="1" t="s">
         <v>5</v>
@@ -4065,19 +4065,19 @@
     </row>
     <row r="17" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -4087,7 +4087,7 @@
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="N17" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O17" s="1" t="s">
         <v>5</v>
@@ -4095,19 +4095,19 @@
     </row>
     <row r="18" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -4118,7 +4118,7 @@
       <c r="L18" s="1"/>
       <c r="M18" s="5"/>
       <c r="N18" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>5</v>
@@ -4126,19 +4126,19 @@
     </row>
     <row r="19" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -4149,7 +4149,7 @@
       <c r="L19" s="1"/>
       <c r="M19" s="5"/>
       <c r="N19" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O19" s="1" t="s">
         <v>5</v>
@@ -4157,32 +4157,32 @@
     </row>
     <row r="20" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="5"/>
       <c r="N20" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>5</v>
@@ -4190,32 +4190,32 @@
     </row>
     <row r="21" spans="1:15" ht="58" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="5"/>
       <c r="N21" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>5</v>
@@ -4223,19 +4223,19 @@
     </row>
     <row r="22" spans="1:15" ht="58" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -4243,12 +4243,12 @@
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="5"/>
       <c r="N22" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O22" s="1" t="s">
         <v>5</v>
@@ -4256,19 +4256,19 @@
     </row>
     <row r="23" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
@@ -4277,11 +4277,11 @@
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M23" s="5"/>
       <c r="N23" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O23" s="1" t="s">
         <v>5</v>
@@ -4289,19 +4289,19 @@
     </row>
     <row r="24" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -4312,7 +4312,7 @@
       <c r="L24" s="1"/>
       <c r="M24" s="5"/>
       <c r="N24" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O24" s="1" t="s">
         <v>5</v>
@@ -4320,19 +4320,19 @@
     </row>
     <row r="25" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -4343,7 +4343,7 @@
       <c r="L25" s="1"/>
       <c r="M25" s="5"/>
       <c r="N25" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O25" s="1" t="s">
         <v>5</v>
@@ -4351,19 +4351,19 @@
     </row>
     <row r="26" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -4373,7 +4373,7 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="N26" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O26" s="1" t="s">
         <v>5</v>
@@ -4381,24 +4381,24 @@
     </row>
     <row r="27" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -4406,7 +4406,7 @@
       <c r="L27" s="1"/>
       <c r="M27" s="5"/>
       <c r="N27" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O27" s="1" t="s">
         <v>5</v>
@@ -4414,19 +4414,19 @@
     </row>
     <row r="28" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
@@ -4437,7 +4437,7 @@
       <c r="L28" s="1"/>
       <c r="M28" s="5"/>
       <c r="N28" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O28" s="1" t="s">
         <v>5</v>
@@ -4445,19 +4445,19 @@
     </row>
     <row r="29" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
@@ -4468,7 +4468,7 @@
       <c r="L29" s="1"/>
       <c r="M29" s="5"/>
       <c r="N29" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O29" s="1" t="s">
         <v>5</v>
@@ -4476,31 +4476,31 @@
     </row>
     <row r="30" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="N30" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O30" s="1" t="s">
         <v>5</v>
@@ -4508,32 +4508,32 @@
     </row>
     <row r="31" spans="1:15" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="5"/>
       <c r="N31" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O31" s="1" t="s">
         <v>5</v>
@@ -4541,19 +4541,19 @@
     </row>
     <row r="32" spans="1:15" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
@@ -4564,7 +4564,7 @@
       <c r="L32" s="1"/>
       <c r="M32" s="5"/>
       <c r="N32" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O32" s="1" t="s">
         <v>5</v>
@@ -4572,19 +4572,19 @@
     </row>
     <row r="33" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -4595,7 +4595,7 @@
       <c r="L33" s="1"/>
       <c r="M33" s="5"/>
       <c r="N33" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O33" s="1" t="s">
         <v>5</v>
@@ -4603,19 +4603,19 @@
     </row>
     <row r="34" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -4626,7 +4626,7 @@
       <c r="L34" s="1"/>
       <c r="M34" s="5"/>
       <c r="N34" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O34" s="1" t="s">
         <v>5</v>
@@ -4634,19 +4634,19 @@
     </row>
     <row r="35" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -4657,7 +4657,7 @@
       <c r="L35" s="1"/>
       <c r="M35" s="5"/>
       <c r="N35" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O35" s="1" t="s">
         <v>5</v>
@@ -4665,19 +4665,19 @@
     </row>
     <row r="36" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C36" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D36" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="D36" s="9" t="s">
-        <v>78</v>
-      </c>
       <c r="E36" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -4688,7 +4688,7 @@
       <c r="L36" s="1"/>
       <c r="M36" s="5"/>
       <c r="N36" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O36" s="1" t="s">
         <v>5</v>
@@ -4696,24 +4696,24 @@
     </row>
     <row r="37" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
@@ -4721,7 +4721,7 @@
       <c r="L37" s="1"/>
       <c r="M37" s="5"/>
       <c r="N37" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O37" s="1" t="s">
         <v>5</v>
@@ -4729,19 +4729,19 @@
     </row>
     <row r="38" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -4752,7 +4752,7 @@
       <c r="L38" s="1"/>
       <c r="M38" s="5"/>
       <c r="N38" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O38" s="1" t="s">
         <v>5</v>
@@ -4760,19 +4760,19 @@
     </row>
     <row r="39" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -4783,7 +4783,7 @@
       <c r="L39" s="1"/>
       <c r="M39" s="5"/>
       <c r="N39" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O39" s="1" t="s">
         <v>5</v>
@@ -4791,32 +4791,32 @@
     </row>
     <row r="40" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="5"/>
       <c r="N40" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O40" s="1" t="s">
         <v>5</v>
@@ -4824,32 +4824,32 @@
     </row>
     <row r="41" spans="1:15" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="5"/>
       <c r="N41" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O41" s="1" t="s">
         <v>5</v>
@@ -4857,19 +4857,19 @@
     </row>
     <row r="42" spans="1:15" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -4880,7 +4880,7 @@
       <c r="L42" s="1"/>
       <c r="M42" s="5"/>
       <c r="N42" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O42" s="1" t="s">
         <v>5</v>
@@ -4888,19 +4888,19 @@
     </row>
     <row r="43" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -4911,7 +4911,7 @@
       <c r="L43" s="1"/>
       <c r="M43" s="5"/>
       <c r="N43" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O43" s="1" t="s">
         <v>5</v>
@@ -4919,19 +4919,19 @@
     </row>
     <row r="44" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -4942,7 +4942,7 @@
       <c r="L44" s="1"/>
       <c r="M44" s="5"/>
       <c r="N44" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O44" s="1" t="s">
         <v>5</v>
@@ -4950,19 +4950,19 @@
     </row>
     <row r="45" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -4973,7 +4973,7 @@
       <c r="L45" s="1"/>
       <c r="M45" s="5"/>
       <c r="N45" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O45" s="1" t="s">
         <v>5</v>
